--- a/banco_de_massas.xlsx
+++ b/banco_de_massas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeltaV\Documents\Eliton Sena de Souza\CM-Calc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeltaV\Documents\Eliton Sena de Souza\CenterOfMass-Calculator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD5CB75-9F8B-4DCD-9D9A-822D83430AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CACFD37-3829-4EB1-9572-2C6A2671CF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,105 +33,126 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
-  <si>
-    <t>ChavetaDir:1</t>
-  </si>
-  <si>
-    <t>ChavetaEsq:1</t>
-  </si>
-  <si>
-    <t>Encaixe Inferior:1</t>
-  </si>
-  <si>
-    <t>Encaixe Superior:1</t>
-  </si>
-  <si>
-    <t>Fix GPS</t>
-  </si>
-  <si>
-    <t>Fix Pixhawk1</t>
-  </si>
-  <si>
-    <t>Fix Pixhawk2</t>
-  </si>
-  <si>
-    <t>Fix Rasp1</t>
-  </si>
-  <si>
-    <t>Fix Rasp2</t>
-  </si>
-  <si>
-    <t>Fix SafetySwitch</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+  <si>
+    <t>nome</t>
+  </si>
+  <si>
+    <t>massa</t>
+  </si>
+  <si>
+    <t>MainPlate</t>
   </si>
   <si>
     <t>Fix Telemetry</t>
   </si>
   <si>
-    <t>Fixação Arducam</t>
-  </si>
-  <si>
-    <t>Inferior:1</t>
-  </si>
-  <si>
-    <t>M. Francesa Direita</t>
-  </si>
-  <si>
-    <t>M. Francesa Esquerda</t>
-  </si>
-  <si>
-    <t>Main Plate</t>
-  </si>
-  <si>
-    <t>Pixhawk 2.4.8 (1):1</t>
+    <t>Fix RC</t>
+  </si>
+  <si>
+    <t>Fix GPS+PWM</t>
+  </si>
+  <si>
+    <t>Mão Francesa Esq</t>
+  </si>
+  <si>
+    <t>Mão Francesa Dir</t>
+  </si>
+  <si>
+    <t>Pixhawk 6C PRO:1</t>
+  </si>
+  <si>
+    <t>Telemetria:1</t>
   </si>
   <si>
     <t>RC Receiver:1</t>
   </si>
   <si>
-    <t>RaspberryPi 5:1</t>
-  </si>
-  <si>
-    <t>SafetySwitch:1</t>
-  </si>
-  <si>
-    <t>Superior:1</t>
-  </si>
-  <si>
-    <t>Suporte Servo:1</t>
-  </si>
-  <si>
-    <t>Tampa + Braço</t>
-  </si>
-  <si>
-    <t>Telemetria:1</t>
-  </si>
-  <si>
-    <t>Topo</t>
-  </si>
-  <si>
-    <t>Fix RC</t>
-  </si>
-  <si>
-    <t>GPS M8N:1</t>
-  </si>
-  <si>
-    <t>DISSIPADOR:1</t>
-  </si>
-  <si>
-    <t>DISSIPADOR:2</t>
-  </si>
-  <si>
-    <t>DISSIPADOR:3</t>
-  </si>
-  <si>
-    <t>DISSIPADOR:4</t>
-  </si>
-  <si>
-    <t>Arducam:1</t>
-  </si>
-  <si>
-    <t>MG90S:1</t>
+    <t>PWM Module:1</t>
+  </si>
+  <si>
+    <t>PWM Module(Espelhar):1</t>
+  </si>
+  <si>
+    <t>GPS M9N:1</t>
+  </si>
+  <si>
+    <t>RPI5 + Case:1</t>
+  </si>
+  <si>
+    <t>Presilha1</t>
+  </si>
+  <si>
+    <t>Presilha2</t>
+  </si>
+  <si>
+    <t>Presilha3</t>
+  </si>
+  <si>
+    <t>Presilha4</t>
+  </si>
+  <si>
+    <t>FixPixhawk TE</t>
+  </si>
+  <si>
+    <t>FixPixhawk TD</t>
+  </si>
+  <si>
+    <t>FixPixhawk BE</t>
+  </si>
+  <si>
+    <t>FixPixhawk BD</t>
+  </si>
+  <si>
+    <t>Sustentáculo (Topo)</t>
+  </si>
+  <si>
+    <t>Antivibração:1</t>
+  </si>
+  <si>
+    <t>Gimbal:1</t>
+  </si>
+  <si>
+    <t>ESC 40A:1</t>
+  </si>
+  <si>
+    <t>ESC 40A:2</t>
+  </si>
+  <si>
+    <t>ESC 40A:3</t>
+  </si>
+  <si>
+    <t>ESC 40A:4</t>
+  </si>
+  <si>
+    <t>PDB:1</t>
+  </si>
+  <si>
+    <t>Braço:1</t>
+  </si>
+  <si>
+    <t>Braço:2</t>
+  </si>
+  <si>
+    <t>Braço:3</t>
+  </si>
+  <si>
+    <t>Braço:4</t>
+  </si>
+  <si>
+    <t>Perna:1</t>
+  </si>
+  <si>
+    <t>Perna:2</t>
+  </si>
+  <si>
+    <t>Perna:3</t>
+  </si>
+  <si>
+    <t>Perna:4</t>
+  </si>
+  <si>
+    <t>Centro:1</t>
   </si>
   <si>
     <t>Alça Direita:1</t>
@@ -140,29 +161,65 @@
     <t>Alça Esquerda:1</t>
   </si>
   <si>
+    <t>Gaveta:1</t>
+  </si>
+  <si>
     <t>Bateria:1</t>
   </si>
   <si>
-    <t>Frame:1</t>
-  </si>
-  <si>
-    <t>Suporte Inferior (Gaveta):1</t>
-  </si>
-  <si>
     <t>Voltímetro:1</t>
   </si>
   <si>
-    <t>nome</t>
-  </si>
-  <si>
-    <t>massa</t>
+    <t>Fix Vreg:1</t>
+  </si>
+  <si>
+    <t>Regulador de Tensão:1</t>
+  </si>
+  <si>
+    <t>Fix OpticalFlow:1</t>
+  </si>
+  <si>
+    <t>OpticalFlow:1</t>
+  </si>
+  <si>
+    <t>Motor CCW:1</t>
+  </si>
+  <si>
+    <t>Motor CCW:2</t>
+  </si>
+  <si>
+    <t>Motor CW:1</t>
+  </si>
+  <si>
+    <t>Motor CW:2</t>
+  </si>
+  <si>
+    <t>Guia:1</t>
+  </si>
+  <si>
+    <t>Guia(Espelhar):1</t>
+  </si>
+  <si>
+    <t>Gancho:1</t>
+  </si>
+  <si>
+    <t>Gaiola:1</t>
+  </si>
+  <si>
+    <t>Pistão:1</t>
+  </si>
+  <si>
+    <t>Horn:1</t>
+  </si>
+  <si>
+    <t>Servo:1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -180,6 +237,11 @@
     <font>
       <u/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -204,10 +266,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -542,332 +605,487 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D59"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.109375" style="1" customWidth="1"/>
     <col min="3" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3">
+        <v>197.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="1">
+        <v>32.9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="1">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="1">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="1">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="1">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1">
         <v>39</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="1">
-        <v>66.957366239999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="1">
-        <v>66.957366239999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="1">
-        <v>18.7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="1">
-        <v>504.4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="1">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="1">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="1">
+        <v>111.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="1">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="1">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="1">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="1">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="1">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="1">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="1">
+        <v>87.6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="1">
+        <v>87.6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="1">
+        <v>87.6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="1">
+        <v>87.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="1">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="1">
-        <v>0.23902363999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="B31" s="1">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="1">
-        <v>0.23902363999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="1">
-        <v>0.23902363999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="1">
-        <v>0.23902363999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" s="1">
-        <v>0.56000000000000005</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="1">
-        <v>0.56000000000000005</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="1">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="1">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="1">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="1">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="1">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="1">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="1">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="1">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" s="1">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="2">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="1">
-        <v>39.4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="1">
-        <v>20.440000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" s="1">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" s="1">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="1">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" s="1">
-        <v>177.4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B30" s="1">
-        <v>40.700000000000003</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B31" s="1">
-        <v>13.7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="B32" s="1">
-        <v>50</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B33" s="1">
-        <v>4.5</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B34" s="1">
-        <v>20.75</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B35" s="1">
-        <v>145.47809828000001</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B36" s="1">
-        <v>6.63</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B37" s="1">
-        <v>5.4</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B38" s="1">
-        <v>26.5</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="B39" s="1">
-        <v>15.48</v>
+        <v>65.599999999999994</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" s="1">
+        <v>65.599999999999994</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="1">
+        <v>65.599999999999994</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="1">
-        <v>11.4</v>
+      <c r="B42" s="1">
+        <v>65.599999999999994</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B43" s="1">
+        <v>99.8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B44" s="1">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B45" s="1">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" s="1">
+        <v>118.6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B47" s="1">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B48" s="1">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B49" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B50" s="1">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B51" s="1">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B52" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B55" s="1">
+        <v>53.7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B56" s="1">
+        <v>60.11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B58" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B59" s="1">
+        <v>10.199999999999999</v>
       </c>
     </row>
   </sheetData>
